--- a/sources/lee_step3.xlsx
+++ b/sources/lee_step3.xlsx
@@ -690,6 +690,11 @@
           <t>When done with 2+4 against Bryan, he will laugh back at Lee and sometimes gain a little energy back.</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>b066f77f-2cf9-45e9-ae19-41234876127b</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>b066f77f-2cf9-45e9-ae19-41234876127b</t>
@@ -727,6 +732,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>b186cd07-1f81-4494-bf28-78196461652c</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>b186cd07-1f81-4494-bf28-78196461652c</t>
@@ -762,6 +772,11 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>9736f543-5f0b-4d41-9d88-4dba289c8e13</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -6382,6 +6397,11 @@
       <c r="I128" t="inlineStr">
         <is>
           <t>mhmhhLhhhm</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>5508724d-2532-494e-91ba-e198355b8ea4</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
